--- a/rules/CORE-000177/negative/01/data/unit-test-coreid-CG0227-negative 1.xlsx
+++ b/rules/CORE-000177/negative/01/data/unit-test-coreid-CG0227-negative 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\Verisian\core-contributor\rules\CORE-000177\negative\01\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000177\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114EE457-BF4F-4442-BF2C-AB7F8D2158C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793A0C84-4A1E-41ED-AB91-A4C9E68B63A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30750" yWindow="1950" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -971,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>142</v>
@@ -980,7 +980,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>116</v>
+      </c>
+      <c r="F2" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -988,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>142</v>
@@ -997,10 +1000,7 @@
         <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F3" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1008,7 +1008,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>142</v>
@@ -1017,7 +1017,10 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>116</v>
+      </c>
+      <c r="F4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1025,7 +1028,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
         <v>142</v>
@@ -1034,10 +1037,7 @@
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
